--- a/arquivos_originais/problem.xlsx
+++ b/arquivos_originais/problem.xlsx
@@ -105,12 +105,14 @@
   <cols>
     <col min="1" max="1" style="10" width="10.0" customWidth="true"/>
     <col min="2" max="2" style="10" width="22.0" customWidth="true"/>
-    <col min="3" max="3" width="10.0" customWidth="true"/>
-    <col min="4" max="4" style="10" width="19.0" customWidth="true"/>
+    <col min="3" max="3" width="18.0" customWidth="true"/>
+    <col min="4" max="4" width="10.0" customWidth="true"/>
     <col min="5" max="5" style="10" width="11.0" customWidth="true"/>
-    <col min="6" max="6" style="10" width="10.0" customWidth="true"/>
-    <col min="7" max="7" width="23.0" customWidth="true"/>
+    <col min="6" max="6" style="10" width="19.0" customWidth="true"/>
+    <col min="7" max="7" style="10" width="10.0" customWidth="true"/>
     <col min="8" max="8" style="10" width="10.0" customWidth="true"/>
+    <col min="9" max="9" style="10" width="10.0" customWidth="true"/>
+    <col min="10" max="10" width="10.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -126,32 +128,42 @@
       </c>
       <c r="C1" s="12" t="inlineStr">
         <is>
+          <t>Aberta</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Atribuído a</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Grupo de atribuição</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
-        <is>
-          <t>Atribuído a</t>
-        </is>
-      </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>IC afetado</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>Incidentes relacionados</t>
-        </is>
-      </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>Marcadores</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Prioridade</t>
         </is>
       </c>
     </row>
@@ -166,14 +178,12 @@
           <t>SISE - AE - ENVIO CREDOR VIDA</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+      <c r="C2" s="6" t="n">
+        <v>46104.628171296295</v>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -183,15 +193,27 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>ANALISE DE SEGURADOS / APOLICES QUE NÃO ESTÃO ENVIANDO A INFORMAÇÃO DE CREDOR AO VIDA.</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
           <t>SISED000</t>
         </is>
       </c>
-      <c r="G2" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>ApoliceEspecifica, PriorAtend0, SISTRAN, SitEmAtendimento</t>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>PriorAtend0, SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
@@ -206,14 +228,12 @@
           <t>Falha dos dados de cliente indevidamente no APP BSC</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+      <c r="C3" s="6" t="n">
+        <v>46078.590532407405</v>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
@@ -223,15 +243,31 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificado falha na unicidade ao obter dados de cliente por meio do APP BSC ao levantar apólices por meio do CPF. 
+No problema deve ser avaliado:
+1 - Avaliar a utilização no acesso as tabelas por meio de chave única ou composta das apólice de faturamento de apólices empresariais. 
+2 - Levantar programas que podem estar sendo utilizadas sem a utilização de chave complementar. 
+3 - Levantar possíveis apólice com concorrência de numeração de chaves. </t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
           <t>SISE-ApoliceVida</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>AguardaAnalistaVIDA, SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
@@ -246,14 +282,12 @@
           <t>QE382 - 6866</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+      <c r="C4" s="6" t="n">
+        <v>45986.45849537037</v>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -263,15 +297,27 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>O cancelamento esta saindo em ramo divergente no QE</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
           <t>SISED000</t>
         </is>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>AguardaAnalistaVIDA, Atuarial, PriorAtend3, SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
@@ -286,14 +332,12 @@
           <t>ABEND PP_SISE1005_D</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+      <c r="C5" s="6" t="n">
+        <v>46105.391747685186</v>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -303,117 +347,147 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Chave duplicada na APL_VIDA_AE_BENEF, ocasionando erro na execução do job 1005.</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
           <t>PP_SISE1005_D</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>ApoliceEspecifica, SISTRAN, SitEmAtendimento</t>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>2 - Alto(a)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>PRB0069017</t>
+          <t>PRB0068967</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>SISE - AE - VIDA - (Código CPD Vida)</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+          <t xml:space="preserve">Seguros prestamista sem recuperação no cancelamento. </t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>46094.6271412037</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>BARBARA PENALVA MONTEIRO</t>
+          <t>DIOGO DA FRANCA RODRIGUES</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>SISED000</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>0.0</v>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seguros prestamista sem recuperação no cancelamento. Necessário levantar apólices que tiveram emissão a partir do aumento do percentual para pagamento de corretor Bradescor em  17/11/2025, com cancelamento e estorno onde não ocorreu recuperação. </t>
+        </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>AguardaImplantacao, ApoliceEspecifica, SISTRAN, SitEmAtendimento</t>
+          <t>D5310S018.corp.bradesco.com.br</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Comissao, SISTRAN</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PRB0068957</t>
+          <t>PRB0069054</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificado que apólices do produto da Scania tiveram aumento de capital maior do que a variação do índice. </t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+          <t>ESTEIRA AUTOMÁTICA NÃO ESTÁ REGISTRANDO AS ALTERAÇÕES REALIZADA NO AVISO NA ABA HISTORICO DE SINISTRO</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>46098.364386574074</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>DIOGO DA FRANCA RODRIGUES</t>
+          <t>ELTON EIDT</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>PP_SISE1016_D</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>0.0</v>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>ESTEIRA AUTOMÁTICA NÃO ESTÁ REGISTRANDO AS ALTERAÇÕES REALIZADAS DE FORMA MANUAL NO AVISO, NA ABA HISTORICO DE SINISTRO.</t>
+        </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>SISTRAN, SitEmAtendimento</t>
+          <t>SISE-SinistroRegulacao</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>PriorAtend2, SinistroNegocio, SISTRAN</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>PRB0065581</t>
+          <t>PRB0064019</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>PROPOSTA RESTITUIDA COM PAGAMENTO DE RESGATE</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+          <t xml:space="preserve">Falta de geração de cobrança para scania. </t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>45916.86949074074</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -423,117 +497,151 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARA PARCERIA DA SCANIA NÃO HOUVE A GERAÇÃO DE PARCELAS PARA O CLIENTE O QUE ESTA CAUSANDO BAU FINANCEIRO, UMA VEZ QUE HÁ O REPASSE DO VALOR MAIS NÃO TEMOS A PARCELA PARA BAIXAR.
+</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
           <t>SISED000</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>AguardaAnalistaVIDA, Resgate, SISTRAN, SitEmAtendimento</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>AguardaAnalistaVIDA, Prestamista, SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PRB0064629</t>
+          <t>PRB0069017</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">erro ao enviar registro de cosseguro ao sap </t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Correção em andamento</t>
-        </is>
+          <t>SISE - AE - VIDA - (Código CPD Vida)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>46097.46923611111</v>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>ANDRE ANDRADE ALEXANDRE ROCHA</t>
+          <t>BARBARA PENALVA MONTEIRO</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>ATUALMENTE A ROTINA ENVIA O CPD COM BASE NA ESTRUTURA COMERCIAL, PEGANDO O MAX ID DO CORRETOR.
+É NECESSARIO ALTERAR O ENVIO DESTE CAMPO PARA O APOLICE ESPECIFICA, FAZENDO A ROTINA EXTRAIR A INFORMAÇÃO DA REGRA CADASTRADA NO SUBESTIPULANTE.</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
           <t>SISED000</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>AguardaAnalistaVIDA, RegistrosOficiais, SISTRAN, SitEmAtendimento</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>AguardaImplantacao, ApoliceEspecifica, SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>PRB0069090</t>
+          <t>PRB0068989</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>ERRO PARA ABRIR COMUNICADO PORTAL INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+          <t xml:space="preserve">Apólices canceladas/expiradas sendo apresentadas na PMBAC. </t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>46094.83461805555</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>ELTON EIDT</t>
+          <t>DIOGO DA FRANCA RODRIGUES</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>sise-bff-comunicado-sinistro</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>1.0</v>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apólices canceladas/expiradas sendo apresentadas na PMBAC.  
+Identificado multiproteção expirado e presente na PMBAC, necessário identificar demais apólices na mesma situação. 
+Levantado que a apólice da evidencia não consta na tabela tCtrlCertfCanctReatv, utilizada para controle de cancelamento e reativação  e base para o processo de provisão da PVR. </t>
+        </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PriorAtend1, SinistroNegocio, SISTRAN, SitEmAtendimento</t>
+          <t>D5310S018.corp.bradesco.com.br</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Atuarial, PriorAtend2, SISTRAN</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PRB0064019</t>
+          <t>PRB0068957</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falta de geração de cobrança para scania. </t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+          <t xml:space="preserve">Identificado que apólices do produto da Scania tiveram aumento de capital maior do que a variação do índice. </t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>46094.45340277778</v>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -543,215 +651,239 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>SISED000</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>0.0</v>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificado que apólices do produto da Scania tiveram aumento de capital maior do que a variação do índice.
+Foi levantado que o processo de faturamento do produto já contempla o reajuste de capital, e dessa forma os produtos deste processo deveriam ser desconsiderados no processo habitual de apólices massificados. 
+Procedures:
+pMassfExecutaDemaisCobrancas.sql
+Up_Mas_Reenquadramento_Reajuste.sql
+</t>
+        </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>AguardaAnalistaVIDA, Prestamista, SISTRAN, SitEmAtendimento</t>
+          <t>PP_SISE1016_D</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>PRB0068712</t>
+          <t>PRB0065581</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>[BVP-Vida] Melhorias PIVI - NOME SOCIAL</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Avaliar</t>
-        </is>
+          <t>PROPOSTA RESTITUIDA COM PAGAMENTO DE RESGATE</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>45972.35024305555</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - VIDA</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>GEORGE MARTINS CORDEIRO</t>
+          <t>DIOGO DA FRANCA RODRIGUES</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>PISB-Integracao</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>0.0</v>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>após restituição total de prêmios, a provisão/reserva não está sendo zerada.</t>
+        </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>AguardaHomologacao, SISTRAN, SitEmAtendimento</t>
+          <t>SISED000</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>AguardaAnalistaVIDA, Resgate, SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PRB0065412</t>
+          <t>PRB0064629</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>[BVP-NEXT] Timeout GravarModGeral</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+          <t xml:space="preserve">erro ao enviar registro de cosseguro ao sap </t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>45938.43850694445</v>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - BVP - VIDA</t>
+          <t>Correção em andamento</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>ALESSANDRA MONTEIRO DE CASTRO MARQUES</t>
+          <t>ANDRE ANDRADE ALEXANDRE ROCHA</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>bvpnext.bradescoseguros.com.br</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>0.0</v>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>ao enviar o movimento 58 esta ocorrendo erro devido não aplicar o fator da ppng para registro de cosseguro</t>
+        </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>SISTRAN, SitEmAtendimento</t>
+          <t>SISED000</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>AguardaAnalistaVIDA, RegistrosOficiais, SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>PRB0068113</t>
+          <t>PRB0069090</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>[PIS] Solicitação de Verificação – Divergência no Status de Propostas Empresariais</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+          <t>ERRO PARA ABRIR COMUNICADO PORTAL INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>46099.33967592593</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - VIDA - PEGA</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>GEORGE MARTINS CORDEIRO</t>
+          <t>ELTON EIDT</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>PISB-Integracao</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0.0</v>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>ERRO PARA ABRIR COMUNICADO PORTAL INSTITUCIONAL</t>
+        </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>SISTRAN, SitEmAtendimento</t>
+          <t>sise-bff-comunicado-sinistro</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>PriorAtend1, SinistroNegocio, SISTRAN, SitEmAtendimento</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PRB0065053</t>
+          <t>PRB0068122</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Atualmente, perguntas de DPS são exibidas em qualquer endosso, inclusive quando há redução do capital segurado. É necessário implementar a regra para que as perguntas sejam exibidas somente quando houver aumento do capital segurado.</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
+          <t>Erro ao salvar a proposta de seguro na BVP.</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>46066.42172453704</v>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>DS - BS - SUSTENTACAO - VIDA - PEGA</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>MARCIO VILELA DE SOUZA</t>
+          <t>DIOGO DA FRANCA RODRIGUES</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>PISB-Integracao</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>1.0</v>
+          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Endpiont de recebimento de proposta está retornando status code 200 com campo numero da proposta null.
+Path do endpoint aonde ocorreu o erro: /SISE-ApoliceVida/api/v2/parceiras/35/produtos/1172/recebimento
+Dados usados no envio da proposta:
+Data e hora do erro:  13/01/2026 - 10:32:50
+CNPJ do Corban: 32392407000106
+CPF do cliente: 89230477591
+Nome do cliente: MARIA CATARINA DA CONCEICAO
+</t>
+        </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>PRB0067540</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Data Pages "D_QuestionOptions" e "D_GenericCommisionValuesList" sendo recarregadas frequentemente.</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>DS - BS - SUSTENTACAO - VIDA - PEGA</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>MARCIO VILELA DE SOUZA</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>d7156lx1274</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>AguardaAnalistaVIDA, SISTRAN, SitEmAtendimento</t>
+          <t>kbnt-bff-in-segurodevida</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>AguardaAnalistaVIDA, SISTRAN</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>

--- a/arquivos_originais/problem.xlsx
+++ b/arquivos_originais/problem.xlsx
@@ -111,8 +111,7 @@
     <col min="6" max="6" style="10" width="19.0" customWidth="true"/>
     <col min="7" max="7" style="10" width="10.0" customWidth="true"/>
     <col min="8" max="8" style="10" width="10.0" customWidth="true"/>
-    <col min="9" max="9" style="10" width="10.0" customWidth="true"/>
-    <col min="10" max="10" width="10.0" customWidth="true"/>
+    <col min="9" max="9" width="10.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -148,20 +147,15 @@
       </c>
       <c r="G1" s="12" t="inlineStr">
         <is>
-          <t>Descrição</t>
+          <t>IC afetado</t>
         </is>
       </c>
       <c r="H1" s="12" t="inlineStr">
         <is>
-          <t>IC afetado</t>
+          <t>Marcadores</t>
         </is>
       </c>
       <c r="I1" s="12" t="inlineStr">
-        <is>
-          <t>Marcadores</t>
-        </is>
-      </c>
-      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>Prioridade</t>
         </is>
@@ -198,20 +192,15 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>ANALISE DE SEGURADOS / APOLICES QUE NÃO ESTÃO ENVIANDO A INFORMAÇÃO DE CREDOR AO VIDA.</t>
+          <t>SISED000</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>SISED000</t>
+          <t>PriorAtend0, SISTRAN, SitEmAtendimento</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>PriorAtend0, SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -248,24 +237,15 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificado falha na unicidade ao obter dados de cliente por meio do APP BSC ao levantar apólices por meio do CPF. 
-No problema deve ser avaliado:
-1 - Avaliar a utilização no acesso as tabelas por meio de chave única ou composta das apólice de faturamento de apólices empresariais. 
-2 - Levantar programas que podem estar sendo utilizadas sem a utilização de chave complementar. 
-3 - Levantar possíveis apólice com concorrência de numeração de chaves. </t>
+          <t>SISE-ApoliceVida</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>SISE-ApoliceVida</t>
+          <t>AguardaAnalistaVIDA, SISTRAN, SitEmAtendimento</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>AguardaAnalistaVIDA, SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -302,20 +282,15 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>O cancelamento esta saindo em ramo divergente no QE</t>
+          <t>SISED000</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>SISED000</t>
+          <t>AguardaAnalistaVIDA, Atuarial, PriorAtend3, SISTRAN, SitEmAtendimento</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>AguardaAnalistaVIDA, Atuarial, PriorAtend3, SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -324,16 +299,16 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PRB0069274</t>
+          <t>PRB0068967</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>ABEND PP_SISE1005_D</t>
+          <t xml:space="preserve">Seguros prestamista sem recuperação no cancelamento. </t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>46105.391747685186</v>
+        <v>46094.6271412037</v>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
@@ -342,7 +317,7 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>JOAO VITOR ALTOMAR</t>
+          <t>DIOGO DA FRANCA RODRIGUES</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -352,38 +327,33 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Chave duplicada na APL_VIDA_AE_BENEF, ocasionando erro na execução do job 1005.</t>
+          <t>D5310S018.corp.bradesco.com.br</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>PP_SISE1005_D</t>
+          <t>Comissao, SISTRAN</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>2 - Alto(a)</t>
+          <t>4 - Baixo(a)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>PRB0068967</t>
+          <t>PRB0069054</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguros prestamista sem recuperação no cancelamento. </t>
+          <t>ESTEIRA AUTOMÁTICA NÃO ESTÁ REGISTRANDO AS ALTERAÇÕES REALIZADA NO AVISO NA ABA HISTORICO DE SINISTRO</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>46094.6271412037</v>
+        <v>46098.364386574074</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
@@ -392,7 +362,7 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>DIOGO DA FRANCA RODRIGUES</t>
+          <t>ELTON EIDT</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -402,20 +372,15 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguros prestamista sem recuperação no cancelamento. Necessário levantar apólices que tiveram emissão a partir do aumento do percentual para pagamento de corretor Bradescor em  17/11/2025, com cancelamento e estorno onde não ocorreu recuperação. </t>
+          <t>SISE-SinistroRegulacao</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>D5310S018.corp.bradesco.com.br</t>
+          <t>PriorAtend2, SinistroNegocio, SISTRAN</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Comissao, SISTRAN</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -424,16 +389,16 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PRB0069054</t>
+          <t>PRB0064019</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>ESTEIRA AUTOMÁTICA NÃO ESTÁ REGISTRANDO AS ALTERAÇÕES REALIZADA NO AVISO NA ABA HISTORICO DE SINISTRO</t>
+          <t xml:space="preserve">Falta de geração de cobrança para scania. </t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>46098.364386574074</v>
+        <v>45916.86949074074</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
@@ -442,7 +407,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>ELTON EIDT</t>
+          <t>DIOGO DA FRANCA RODRIGUES</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -452,20 +417,15 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>ESTEIRA AUTOMÁTICA NÃO ESTÁ REGISTRANDO AS ALTERAÇÕES REALIZADAS DE FORMA MANUAL NO AVISO, NA ABA HISTORICO DE SINISTRO.</t>
+          <t>SISED000</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>SISE-SinistroRegulacao</t>
+          <t>AguardaAnalistaVIDA, Prestamista, SISTRAN, SitEmAtendimento</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>PriorAtend2, SinistroNegocio, SISTRAN</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -474,16 +434,16 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>PRB0064019</t>
+          <t>PRB0069017</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falta de geração de cobrança para scania. </t>
+          <t>SISE - AE - VIDA - (Código CPD Vida)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>45916.86949074074</v>
+        <v>46097.46923611111</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -492,7 +452,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>DIOGO DA FRANCA RODRIGUES</t>
+          <t>BARBARA PENALVA MONTEIRO</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -502,21 +462,15 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARA PARCERIA DA SCANIA NÃO HOUVE A GERAÇÃO DE PARCELAS PARA O CLIENTE O QUE ESTA CAUSANDO BAU FINANCEIRO, UMA VEZ QUE HÁ O REPASSE DO VALOR MAIS NÃO TEMOS A PARCELA PARA BAIXAR.
-</t>
+          <t>SISED000</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>SISED000</t>
+          <t>AguardaImplantacao, ApoliceEspecifica, SISTRAN, SitEmAtendimento</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>AguardaAnalistaVIDA, Prestamista, SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -525,16 +479,16 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PRB0069017</t>
+          <t>PRB0068989</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>SISE - AE - VIDA - (Código CPD Vida)</t>
+          <t xml:space="preserve">Apólices canceladas/expiradas sendo apresentadas na PMBAC. </t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>46097.46923611111</v>
+        <v>46094.83461805555</v>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
@@ -543,7 +497,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>BARBARA PENALVA MONTEIRO</t>
+          <t>DIOGO DA FRANCA RODRIGUES</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -553,21 +507,15 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>ATUALMENTE A ROTINA ENVIA O CPD COM BASE NA ESTRUTURA COMERCIAL, PEGANDO O MAX ID DO CORRETOR.
-É NECESSARIO ALTERAR O ENVIO DESTE CAMPO PARA O APOLICE ESPECIFICA, FAZENDO A ROTINA EXTRAIR A INFORMAÇÃO DA REGRA CADASTRADA NO SUBESTIPULANTE.</t>
+          <t>D5310S018.corp.bradesco.com.br</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>SISED000</t>
+          <t>Atuarial, PriorAtend2, SISTRAN</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>AguardaImplantacao, ApoliceEspecifica, SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -576,16 +524,16 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>PRB0068989</t>
+          <t>PRB0068957</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apólices canceladas/expiradas sendo apresentadas na PMBAC. </t>
+          <t xml:space="preserve">Identificado que apólices do produto da Scania tiveram aumento de capital maior do que a variação do índice. </t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>46094.83461805555</v>
+        <v>46094.45340277778</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -604,22 +552,15 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apólices canceladas/expiradas sendo apresentadas na PMBAC.  
-Identificado multiproteção expirado e presente na PMBAC, necessário identificar demais apólices na mesma situação. 
-Levantado que a apólice da evidencia não consta na tabela tCtrlCertfCanctReatv, utilizada para controle de cancelamento e reativação  e base para o processo de provisão da PVR. </t>
+          <t>PP_SISE1016_D</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>D5310S018.corp.bradesco.com.br</t>
+          <t>SISTRAN, SitEmAtendimento</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Atuarial, PriorAtend2, SISTRAN</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -628,16 +569,16 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PRB0068957</t>
+          <t>PRB0065581</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificado que apólices do produto da Scania tiveram aumento de capital maior do que a variação do índice. </t>
+          <t>PROPOSTA RESTITUIDA COM PAGAMENTO DE RESGATE</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>46094.45340277778</v>
+        <v>45972.35024305555</v>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
@@ -656,25 +597,15 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificado que apólices do produto da Scania tiveram aumento de capital maior do que a variação do índice.
-Foi levantado que o processo de faturamento do produto já contempla o reajuste de capital, e dessa forma os produtos deste processo deveriam ser desconsiderados no processo habitual de apólices massificados. 
-Procedures:
-pMassfExecutaDemaisCobrancas.sql
-Up_Mas_Reenquadramento_Reajuste.sql
-</t>
+          <t>SISED000</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>PP_SISE1016_D</t>
+          <t>AguardaAnalistaVIDA, Resgate, SISTRAN, SitEmAtendimento</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -683,25 +614,25 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>PRB0065581</t>
+          <t>PRB0064629</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>PROPOSTA RESTITUIDA COM PAGAMENTO DE RESGATE</t>
+          <t xml:space="preserve">erro ao enviar registro de cosseguro ao sap </t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>45972.35024305555</v>
+        <v>45938.43850694445</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Análise de causa raiz</t>
+          <t>Correção em andamento</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>DIOGO DA FRANCA RODRIGUES</t>
+          <t>ANDRE ANDRADE ALEXANDRE ROCHA</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -711,20 +642,15 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>após restituição total de prêmios, a provisão/reserva não está sendo zerada.</t>
+          <t>SISED000</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>SISED000</t>
+          <t>AguardaAnalistaVIDA, RegistrosOficiais, SISTRAN, SitEmAtendimento</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>AguardaAnalistaVIDA, Resgate, SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -733,25 +659,25 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PRB0064629</t>
+          <t>PRB0069090</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">erro ao enviar registro de cosseguro ao sap </t>
+          <t>ERRO PARA ABRIR COMUNICADO PORTAL INSTITUCIONAL</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>45938.43850694445</v>
+        <v>46099.33967592593</v>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Correção em andamento</t>
+          <t>Análise de causa raiz</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>ANDRE ANDRADE ALEXANDRE ROCHA</t>
+          <t>ELTON EIDT</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -761,20 +687,15 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>ao enviar o movimento 58 esta ocorrendo erro devido não aplicar o fator da ppng para registro de cosseguro</t>
+          <t>sise-bff-comunicado-sinistro</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>SISED000</t>
+          <t>PriorAtend1, SinistroNegocio, SISTRAN, SitEmAtendimento</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>AguardaAnalistaVIDA, RegistrosOficiais, SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
@@ -783,16 +704,16 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>PRB0069090</t>
+          <t>PRB0068122</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>ERRO PARA ABRIR COMUNICADO PORTAL INSTITUCIONAL</t>
+          <t>Erro ao salvar a proposta de seguro na BVP.</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>46099.33967592593</v>
+        <v>46066.42172453704</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -801,7 +722,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>ELTON EIDT</t>
+          <t>DIOGO DA FRANCA RODRIGUES</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
@@ -811,77 +732,15 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>ERRO PARA ABRIR COMUNICADO PORTAL INSTITUCIONAL</t>
+          <t>kbnt-bff-in-segurodevida</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>sise-bff-comunicado-sinistro</t>
+          <t>AguardaAnalistaVIDA, SISTRAN</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>PriorAtend1, SinistroNegocio, SISTRAN, SitEmAtendimento</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>4 - Baixo(a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>PRB0068122</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Erro ao salvar a proposta de seguro na BVP.</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>46066.42172453704</v>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Análise de causa raiz</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>DIOGO DA FRANCA RODRIGUES</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>DS - BS - SUSTENTACAO - BVP - SISE-SP</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Endpiont de recebimento de proposta está retornando status code 200 com campo numero da proposta null.
-Path do endpoint aonde ocorreu o erro: /SISE-ApoliceVida/api/v2/parceiras/35/produtos/1172/recebimento
-Dados usados no envio da proposta:
-Data e hora do erro:  13/01/2026 - 10:32:50
-CNPJ do Corban: 32392407000106
-CPF do cliente: 89230477591
-Nome do cliente: MARIA CATARINA DA CONCEICAO
-</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>kbnt-bff-in-segurodevida</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>AguardaAnalistaVIDA, SISTRAN</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>4 - Baixo(a)</t>
         </is>
